--- a/БД/funcs/T2_LVALH.xlsx
+++ b/БД/funcs/T2_LVALH.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="28290" windowHeight="12585" activeTab="2"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="28290" windowHeight="12585"/>
   </bookViews>
   <sheets>
     <sheet name="Controls" sheetId="4" r:id="rId1"/>
@@ -740,7 +740,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -774,6 +774,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -839,7 +845,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1003,17 +1009,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1418,15 +1427,15 @@
       <c r="AW1" s="11"/>
       <c r="AX1" s="11"/>
       <c r="AY1" s="13"/>
-      <c r="AZ1" s="59" t="s">
+      <c r="AZ1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="BA1" s="60"/>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="60"/>
-      <c r="BE1" s="60"/>
-      <c r="BF1" s="60"/>
+      <c r="BA1" s="62"/>
+      <c r="BB1" s="62"/>
+      <c r="BC1" s="62"/>
+      <c r="BD1" s="62"/>
+      <c r="BE1" s="62"/>
+      <c r="BF1" s="62"/>
     </row>
     <row r="2" spans="1:16379" s="22" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -18017,21 +18026,20 @@
       <c r="AS3" s="31">
         <v>0</v>
       </c>
-      <c r="AT3" s="31">
-        <v>0</v>
+      <c r="AT3" s="63">
+        <v>1</v>
       </c>
       <c r="AU3" s="31">
         <v>0</v>
       </c>
-      <c r="AV3" s="31">
-        <f t="shared" ref="AV3" si="2">BIN2DEC(CONCATENATE(0,0,0,0,AR3,AS3,AT3,AU3))</f>
-        <v>0</v>
-      </c>
-      <c r="AW3" s="31">
-        <v>0</v>
-      </c>
-      <c r="AX3" s="31">
-        <v>0</v>
+      <c r="AV3" s="63">
+        <v>1</v>
+      </c>
+      <c r="AW3" s="63">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="63">
+        <v>1</v>
       </c>
       <c r="AY3" s="31"/>
       <c r="AZ3" s="28"/>
@@ -18042,7 +18050,7 @@
       <c r="BE3" s="35"/>
       <c r="BF3" s="31"/>
       <c r="BG3" s="36" t="str">
-        <f t="shared" ref="BG3" si="3">CONCATENATE("description: """,F3,"""", ", ", "note: """,E3,"""",", ","group: """, B3, """",", ","minValue: ", S3,", ","maxValue: ", T3,", ","step: ", U3,", ","units: """, R3, """",", ","defaultValue: ", X3,", ","eventRegistration: ", Y3,)</f>
+        <f t="shared" ref="BG3" si="2">CONCATENATE("description: """,F3,"""", ", ", "note: """,E3,"""",", ","group: """, B3, """",", ","minValue: ", S3,", ","maxValue: ", T3,", ","step: ", U3,", ","units: """, R3, """",", ","defaultValue: ", X3,", ","eventRegistration: ", Y3,)</f>
         <v>description: "Вывод терминала", note: "Вывод терминала", group: "control", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH3" s="37"/>
@@ -18065,7 +18073,7 @@
       </c>
       <c r="H4" s="25"/>
       <c r="I4" s="25">
-        <f t="shared" ref="I4:I6" si="4">LEN(F4)</f>
+        <f t="shared" ref="I4:I6" si="3">LEN(F4)</f>
         <v>12</v>
       </c>
       <c r="J4" s="25" t="str">
@@ -18146,7 +18154,7 @@
         <v>0</v>
       </c>
       <c r="AV4" s="31">
-        <f t="shared" ref="AV4:AV6" si="5">BIN2DEC(CONCATENATE(0,0,0,0,AR4,AS4,AT4,AU4))</f>
+        <f t="shared" ref="AV4:AV6" si="4">BIN2DEC(CONCATENATE(0,0,0,0,AR4,AS4,AT4,AU4))</f>
         <v>0</v>
       </c>
       <c r="AW4" s="31">
@@ -18164,7 +18172,7 @@
       <c r="BE4" s="35"/>
       <c r="BF4" s="31"/>
       <c r="BG4" s="36" t="str">
-        <f t="shared" ref="BG4:BG6" si="6">CONCATENATE("description: """,F4,"""", ", ", "note: """,E4,"""",", ","group: """, B4, """",", ","minValue: ", S4,", ","maxValue: ", T4,", ","step: ", U4,", ","units: """, R4, """",", ","defaultValue: ", X4,", ","eventRegistration: ", Y4,)</f>
+        <f t="shared" ref="BG4:BG6" si="5">CONCATENATE("description: """,F4,"""", ", ", "note: """,E4,"""",", ","group: """, B4, """",", ","minValue: ", S4,", ","maxValue: ", T4,", ","step: ", U4,", ","units: """, R4, """",", ","defaultValue: ", X4,", ","eventRegistration: ", Y4,)</f>
         <v>description: "Сраб.сигн ТО", note: "Срабатывание ТО на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH4" s="37"/>
@@ -18187,7 +18195,7 @@
       </c>
       <c r="H5" s="25"/>
       <c r="I5" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="J5" s="25" t="str">
@@ -18268,7 +18276,7 @@
         <v>0</v>
       </c>
       <c r="AV5" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AW5" s="31">
@@ -18286,7 +18294,7 @@
       <c r="BE5" s="35"/>
       <c r="BF5" s="31"/>
       <c r="BG5" s="36" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>description: "Сраб.сигн МТЗ 1ст.", note: "Срабатывание 1 ступени МТЗ на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH5" s="37"/>
@@ -18309,7 +18317,7 @@
       </c>
       <c r="H6" s="25"/>
       <c r="I6" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="J6" s="25" t="str">
@@ -18390,7 +18398,7 @@
         <v>0</v>
       </c>
       <c r="AV6" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AW6" s="31">
@@ -18408,7 +18416,7 @@
       <c r="BE6" s="35"/>
       <c r="BF6" s="31"/>
       <c r="BG6" s="36" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>description: "Сраб.сигн МТЗ 2ст.", note: "Срабатывание 2 ступени МТЗ на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH6" s="37"/>
@@ -18431,7 +18439,7 @@
       </c>
       <c r="H7" s="25"/>
       <c r="I7" s="25">
-        <f t="shared" ref="I7:I8" si="7">LEN(F7)</f>
+        <f t="shared" ref="I7:I8" si="6">LEN(F7)</f>
         <v>18</v>
       </c>
       <c r="J7" s="25" t="str">
@@ -18512,7 +18520,7 @@
         <v>0</v>
       </c>
       <c r="AV7" s="31">
-        <f t="shared" ref="AV7:AV8" si="8">BIN2DEC(CONCATENATE(0,0,0,0,AR7,AS7,AT7,AU7))</f>
+        <f t="shared" ref="AV7:AV8" si="7">BIN2DEC(CONCATENATE(0,0,0,0,AR7,AS7,AT7,AU7))</f>
         <v>0</v>
       </c>
       <c r="AW7" s="31">
@@ -18530,7 +18538,7 @@
       <c r="BE7" s="35"/>
       <c r="BF7" s="31"/>
       <c r="BG7" s="36" t="str">
-        <f t="shared" ref="BG7:BG8" si="9">CONCATENATE("description: """,F7,"""", ", ", "note: """,E7,"""",", ","group: """, B7, """",", ","minValue: ", S7,", ","maxValue: ", T7,", ","step: ", U7,", ","units: """, R7, """",", ","defaultValue: ", X7,", ","eventRegistration: ", Y7,)</f>
+        <f t="shared" ref="BG7:BG8" si="8">CONCATENATE("description: """,F7,"""", ", ", "note: """,E7,"""",", ","group: """, B7, """",", ","minValue: ", S7,", ","maxValue: ", T7,", ","step: ", U7,", ","units: """, R7, """",", ","defaultValue: ", X7,", ","eventRegistration: ", Y7,)</f>
         <v>description: "Сраб.сигн МТЗ 3ст.", note: "Срабатывание 3 ступени МТЗ на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH7" s="37"/>
@@ -18553,7 +18561,7 @@
       </c>
       <c r="H8" s="25"/>
       <c r="I8" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="J8" s="25" t="str">
@@ -18634,7 +18642,7 @@
         <v>0</v>
       </c>
       <c r="AV8" s="31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AW8" s="31">
@@ -18652,7 +18660,7 @@
       <c r="BE8" s="35"/>
       <c r="BF8" s="31"/>
       <c r="BG8" s="36" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>description: "Сраб.сигн ЛО ГЗсигн", note: "Срабатывание ЛО ГЗсигн на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH8" s="37"/>
@@ -18675,11 +18683,11 @@
       </c>
       <c r="H9" s="25"/>
       <c r="I9" s="25">
-        <f t="shared" ref="I9:I31" si="10">LEN(F9)</f>
+        <f t="shared" ref="I9:I31" si="9">LEN(F9)</f>
         <v>19</v>
       </c>
       <c r="J9" s="25" t="str">
-        <f t="shared" ref="J9:J31" si="11">IF(LEN(F9)&lt;=$J$1,F9,"")</f>
+        <f t="shared" ref="J9:J31" si="10">IF(LEN(F9)&lt;=$J$1,F9,"")</f>
         <v>Сраб.сигн ЛО ГЗоткл</v>
       </c>
       <c r="K9" s="23" t="s">
@@ -18756,7 +18764,7 @@
         <v>0</v>
       </c>
       <c r="AV9" s="31">
-        <f t="shared" ref="AV9:AV31" si="12">BIN2DEC(CONCATENATE(0,0,0,0,AR9,AS9,AT9,AU9))</f>
+        <f t="shared" ref="AV9:AV31" si="11">BIN2DEC(CONCATENATE(0,0,0,0,AR9,AS9,AT9,AU9))</f>
         <v>0</v>
       </c>
       <c r="AW9" s="31">
@@ -18774,7 +18782,7 @@
       <c r="BE9" s="35"/>
       <c r="BF9" s="31"/>
       <c r="BG9" s="36" t="str">
-        <f t="shared" ref="BG9:BG31" si="13">CONCATENATE("description: """,F9,"""", ", ", "note: """,E9,"""",", ","group: """, B9, """",", ","minValue: ", S9,", ","maxValue: ", T9,", ","step: ", U9,", ","units: """, R9, """",", ","defaultValue: ", X9,", ","eventRegistration: ", Y9,)</f>
+        <f t="shared" ref="BG9:BG31" si="12">CONCATENATE("description: """,F9,"""", ", ", "note: """,E9,"""",", ","group: """, B9, """",", ","minValue: ", S9,", ","maxValue: ", T9,", ","step: ", U9,", ","units: """, R9, """",", ","defaultValue: ", X9,", ","eventRegistration: ", Y9,)</f>
         <v>description: "Сраб.сигн ЛО ГЗоткл", note: "Срабатывание ЛО ГЗоткл на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH9" s="37"/>
@@ -18797,11 +18805,11 @@
       </c>
       <c r="H10" s="25"/>
       <c r="I10" s="25">
+        <f t="shared" si="9"/>
+        <v>19</v>
+      </c>
+      <c r="J10" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>19</v>
-      </c>
-      <c r="J10" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Сраб.сигн ЛО ГЗ РПН</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -18878,7 +18886,7 @@
         <v>0</v>
       </c>
       <c r="AV10" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW10" s="31">
@@ -18896,7 +18904,7 @@
       <c r="BE10" s="35"/>
       <c r="BF10" s="31"/>
       <c r="BG10" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Сраб.сигн ЛО ГЗ РПН", note: "Срабатывание ЛО ГЗ РПН на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH10" s="37"/>
@@ -18919,11 +18927,11 @@
       </c>
       <c r="H11" s="25"/>
       <c r="I11" s="25">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="J11" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>8</v>
-      </c>
-      <c r="J11" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Сраб. ЗП</v>
       </c>
       <c r="K11" s="23" t="s">
@@ -19000,7 +19008,7 @@
         <v>0</v>
       </c>
       <c r="AV11" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW11" s="31">
@@ -19018,7 +19026,7 @@
       <c r="BE11" s="35"/>
       <c r="BF11" s="31"/>
       <c r="BG11" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Сраб. ЗП", note: "Срабатывание ЗП", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH11" s="37"/>
@@ -19041,11 +19049,11 @@
       </c>
       <c r="H12" s="25"/>
       <c r="I12" s="25">
+        <f t="shared" si="9"/>
+        <v>13</v>
+      </c>
+      <c r="J12" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>13</v>
-      </c>
-      <c r="J12" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Сраб.сигн ЗОП</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -19122,7 +19130,7 @@
         <v>0</v>
       </c>
       <c r="AV12" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW12" s="31">
@@ -19140,7 +19148,7 @@
       <c r="BE12" s="35"/>
       <c r="BF12" s="31"/>
       <c r="BG12" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Сраб.сигн ЗОП", note: "Срабатывание ЗОП на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH12" s="37"/>
@@ -19163,11 +19171,11 @@
       </c>
       <c r="H13" s="25"/>
       <c r="I13" s="25">
+        <f t="shared" si="9"/>
+        <v>11</v>
+      </c>
+      <c r="J13" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>11</v>
-      </c>
-      <c r="J13" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Неиспр. ЦН1</v>
       </c>
       <c r="K13" s="23" t="s">
@@ -19244,7 +19252,7 @@
         <v>0</v>
       </c>
       <c r="AV13" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW13" s="31">
@@ -19262,7 +19270,7 @@
       <c r="BE13" s="35"/>
       <c r="BF13" s="31"/>
       <c r="BG13" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Неиспр. ЦН1", note: "Неисправность цепей напряжения НН1", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH13" s="37"/>
@@ -19285,11 +19293,11 @@
       </c>
       <c r="H14" s="25"/>
       <c r="I14" s="25">
+        <f t="shared" si="9"/>
+        <v>11</v>
+      </c>
+      <c r="J14" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>11</v>
-      </c>
-      <c r="J14" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Неиспр. ЦН2</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -19366,7 +19374,7 @@
         <v>0</v>
       </c>
       <c r="AV14" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW14" s="31">
@@ -19384,7 +19392,7 @@
       <c r="BE14" s="35"/>
       <c r="BF14" s="31"/>
       <c r="BG14" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Неиспр. ЦН2", note: "Неисправность цепей напряжения НН2", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH14" s="37"/>
@@ -19407,11 +19415,11 @@
       </c>
       <c r="H15" s="25"/>
       <c r="I15" s="25">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="J15" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>10</v>
-      </c>
-      <c r="J15" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Сраб. ЛО Т</v>
       </c>
       <c r="K15" s="23" t="s">
@@ -19488,7 +19496,7 @@
         <v>0</v>
       </c>
       <c r="AV15" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW15" s="31">
@@ -19506,7 +19514,7 @@
       <c r="BE15" s="35"/>
       <c r="BF15" s="31"/>
       <c r="BG15" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Сраб. ЛО Т", note: "Срабатывание общей логики отключения трансформатора", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH15" s="37"/>
@@ -19529,11 +19537,11 @@
       </c>
       <c r="H16" s="25"/>
       <c r="I16" s="25">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="J16" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>10</v>
-      </c>
-      <c r="J16" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Сраб. УРОВ</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -19610,7 +19618,7 @@
         <v>0</v>
       </c>
       <c r="AV16" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW16" s="31">
@@ -19628,7 +19636,7 @@
       <c r="BE16" s="35"/>
       <c r="BF16" s="31"/>
       <c r="BG16" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Сраб. УРОВ", note: "Срабатывание УРОВ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH16" s="37"/>
@@ -19651,11 +19659,11 @@
       </c>
       <c r="H17" s="25"/>
       <c r="I17" s="25">
+        <f t="shared" si="9"/>
+        <v>18</v>
+      </c>
+      <c r="J17" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>18</v>
-      </c>
-      <c r="J17" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Сраб. УРОВ на себя</v>
       </c>
       <c r="K17" s="23" t="s">
@@ -19732,7 +19740,7 @@
         <v>0</v>
       </c>
       <c r="AV17" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW17" s="31">
@@ -19750,7 +19758,7 @@
       <c r="BE17" s="35"/>
       <c r="BF17" s="31"/>
       <c r="BG17" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Сраб. УРОВ на себя", note: "Срабатывание УРОВ &lt;&lt;на себя&gt;&gt;", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH17" s="37"/>
@@ -19773,11 +19781,11 @@
       </c>
       <c r="H18" s="25"/>
       <c r="I18" s="25">
+        <f t="shared" si="9"/>
+        <v>17</v>
+      </c>
+      <c r="J18" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>17</v>
-      </c>
-      <c r="J18" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Превышен ресурс В</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -19854,7 +19862,7 @@
         <v>0</v>
       </c>
       <c r="AV18" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW18" s="31">
@@ -19872,7 +19880,7 @@
       <c r="BE18" s="35"/>
       <c r="BF18" s="31"/>
       <c r="BG18" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Превышен ресурс В", note: "Превышен ресурс выключателя", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH18" s="37"/>
@@ -19895,11 +19903,11 @@
       </c>
       <c r="H19" s="25"/>
       <c r="I19" s="25">
+        <f t="shared" si="9"/>
+        <v>15</v>
+      </c>
+      <c r="J19" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>15</v>
-      </c>
-      <c r="J19" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Неисправность В</v>
       </c>
       <c r="K19" s="23" t="s">
@@ -19976,7 +19984,7 @@
         <v>0</v>
       </c>
       <c r="AV19" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW19" s="31">
@@ -19994,7 +20002,7 @@
       <c r="BE19" s="35"/>
       <c r="BF19" s="31"/>
       <c r="BG19" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Неисправность В", note: "Неисправность выключателя", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH19" s="37"/>
@@ -20017,11 +20025,11 @@
       </c>
       <c r="H20" s="25"/>
       <c r="I20" s="25">
+        <f t="shared" si="9"/>
+        <v>18</v>
+      </c>
+      <c r="J20" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>18</v>
-      </c>
-      <c r="J20" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>В самопр. отключен</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -20098,7 +20106,7 @@
         <v>0</v>
       </c>
       <c r="AV20" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW20" s="31">
@@ -20116,7 +20124,7 @@
       <c r="BE20" s="35"/>
       <c r="BF20" s="31"/>
       <c r="BG20" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "В самопр. отключен", note: "Выключатель самопроизвольно отключен", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH20" s="37"/>
@@ -20139,11 +20147,11 @@
       </c>
       <c r="H21" s="25"/>
       <c r="I21" s="25">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+      <c r="J21" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>7</v>
-      </c>
-      <c r="J21" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>ГЗ сигн</v>
       </c>
       <c r="K21" s="23" t="s">
@@ -20220,7 +20228,7 @@
         <v>0</v>
       </c>
       <c r="AV21" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW21" s="31">
@@ -20238,7 +20246,7 @@
       <c r="BE21" s="35"/>
       <c r="BF21" s="31"/>
       <c r="BG21" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "ГЗ сигн", note: "Сигнализация от ГЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH21" s="37"/>
@@ -20261,11 +20269,11 @@
       </c>
       <c r="H22" s="25"/>
       <c r="I22" s="25">
+        <f t="shared" si="9"/>
+        <v>12</v>
+      </c>
+      <c r="J22" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>12</v>
-      </c>
-      <c r="J22" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Низ.изол. ГЗ</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -20342,7 +20350,7 @@
         <v>0</v>
       </c>
       <c r="AV22" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW22" s="31">
@@ -20360,7 +20368,7 @@
       <c r="BE22" s="35"/>
       <c r="BF22" s="31"/>
       <c r="BG22" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Низ.изол. ГЗ", note: "Низкая изоляция ГЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH22" s="37"/>
@@ -20383,11 +20391,11 @@
       </c>
       <c r="H23" s="25"/>
       <c r="I23" s="25">
+        <f t="shared" si="9"/>
+        <v>16</v>
+      </c>
+      <c r="J23" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>16</v>
-      </c>
-      <c r="J23" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>ГЗ заблокирована</v>
       </c>
       <c r="K23" s="23" t="s">
@@ -20464,7 +20472,7 @@
         <v>0</v>
       </c>
       <c r="AV23" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW23" s="31">
@@ -20482,7 +20490,7 @@
       <c r="BE23" s="35"/>
       <c r="BF23" s="31"/>
       <c r="BG23" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "ГЗ заблокирована", note: "ГЗ заблокирована", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH23" s="37"/>
@@ -20505,11 +20513,11 @@
       </c>
       <c r="H24" s="25"/>
       <c r="I24" s="25">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+      <c r="J24" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>7</v>
-      </c>
-      <c r="J24" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>ОТ сигн</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -20586,7 +20594,7 @@
         <v>0</v>
       </c>
       <c r="AV24" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW24" s="31">
@@ -20604,7 +20612,7 @@
       <c r="BE24" s="35"/>
       <c r="BF24" s="31"/>
       <c r="BG24" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "ОТ сигн", note: "Контроль оперативного тока", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH24" s="37"/>
@@ -20627,11 +20635,11 @@
       </c>
       <c r="H25" s="25"/>
       <c r="I25" s="25">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="J25" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>10</v>
-      </c>
-      <c r="J25" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>ОТ НН сигн</v>
       </c>
       <c r="K25" s="23" t="s">
@@ -20708,7 +20716,7 @@
         <v>0</v>
       </c>
       <c r="AV25" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW25" s="31">
@@ -20726,7 +20734,7 @@
       <c r="BE25" s="35"/>
       <c r="BF25" s="31"/>
       <c r="BG25" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "ОТ НН сигн", note: "Контроль оперативного тока НН", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH25" s="37"/>
@@ -20749,11 +20757,11 @@
       </c>
       <c r="H26" s="25"/>
       <c r="I26" s="25">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="J26" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>10</v>
-      </c>
-      <c r="J26" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Внеш. откл</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -20830,7 +20838,7 @@
         <v>0</v>
       </c>
       <c r="AV26" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW26" s="31">
@@ -20848,7 +20856,7 @@
       <c r="BE26" s="35"/>
       <c r="BF26" s="31"/>
       <c r="BG26" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Внеш. откл", note: "Внешнее отключение", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH26" s="37"/>
@@ -20871,11 +20879,11 @@
       </c>
       <c r="H27" s="25"/>
       <c r="I27" s="25">
+        <f t="shared" si="9"/>
+        <v>18</v>
+      </c>
+      <c r="J27" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>18</v>
-      </c>
-      <c r="J27" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Вых.цепи разобраны</v>
       </c>
       <c r="K27" s="23" t="s">
@@ -20952,7 +20960,7 @@
         <v>0</v>
       </c>
       <c r="AV27" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW27" s="31">
@@ -20970,7 +20978,7 @@
       <c r="BE27" s="35"/>
       <c r="BF27" s="31"/>
       <c r="BG27" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Вых.цепи разобраны", note: "Выходные цепи разобраны", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH27" s="37"/>
@@ -20993,11 +21001,11 @@
       </c>
       <c r="H28" s="25"/>
       <c r="I28" s="25">
+        <f t="shared" si="9"/>
+        <v>11</v>
+      </c>
+      <c r="J28" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>11</v>
-      </c>
-      <c r="J28" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>БИ выведены</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -21074,7 +21082,7 @@
         <v>0</v>
       </c>
       <c r="AV28" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW28" s="31">
@@ -21092,7 +21100,7 @@
       <c r="BE28" s="35"/>
       <c r="BF28" s="31"/>
       <c r="BG28" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "БИ выведены", note: "БИ выведены", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH28" s="37"/>
@@ -21115,11 +21123,11 @@
       </c>
       <c r="H29" s="25"/>
       <c r="I29" s="25">
+        <f t="shared" si="9"/>
+        <v>17</v>
+      </c>
+      <c r="J29" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>17</v>
-      </c>
-      <c r="J29" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Прев. вр. пер. КА</v>
       </c>
       <c r="K29" s="23" t="s">
@@ -21196,7 +21204,7 @@
         <v>0</v>
       </c>
       <c r="AV29" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW29" s="31">
@@ -21214,7 +21222,7 @@
       <c r="BE29" s="35"/>
       <c r="BF29" s="31"/>
       <c r="BG29" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Прев. вр. пер. КА", note: "Превышение времени переключения КА", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH29" s="37"/>
@@ -21237,11 +21245,11 @@
       </c>
       <c r="H30" s="25"/>
       <c r="I30" s="25">
+        <f t="shared" si="9"/>
+        <v>19</v>
+      </c>
+      <c r="J30" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>19</v>
-      </c>
-      <c r="J30" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>Общ. внеш. сигн. СС</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -21318,7 +21326,7 @@
         <v>0</v>
       </c>
       <c r="AV30" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW30" s="31">
@@ -21336,7 +21344,7 @@
       <c r="BE30" s="35"/>
       <c r="BF30" s="31"/>
       <c r="BG30" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "Общ. внеш. сигн. СС", note: "Общий внешний сигнал от СС", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH30" s="37"/>
@@ -21359,11 +21367,11 @@
       </c>
       <c r="H31" s="25"/>
       <c r="I31" s="25">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="J31" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="J31" s="25" t="str">
-        <f t="shared" si="11"/>
         <v>IRF</v>
       </c>
       <c r="K31" s="23" t="s">
@@ -21440,7 +21448,7 @@
         <v>0</v>
       </c>
       <c r="AV31" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW31" s="31">
@@ -21458,7 +21466,7 @@
       <c r="BE31" s="35"/>
       <c r="BF31" s="31"/>
       <c r="BG31" s="36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>description: "IRF", note: "Неисправность терминала", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH31" s="37"/>
@@ -25299,15 +25307,15 @@
       <c r="AW1" s="11"/>
       <c r="AX1" s="11"/>
       <c r="AY1" s="13"/>
-      <c r="AZ1" s="59" t="s">
+      <c r="AZ1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="BA1" s="60"/>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="60"/>
-      <c r="BE1" s="60"/>
-      <c r="BF1" s="60"/>
+      <c r="BA1" s="62"/>
+      <c r="BB1" s="62"/>
+      <c r="BC1" s="62"/>
+      <c r="BD1" s="62"/>
+      <c r="BE1" s="62"/>
+      <c r="BF1" s="62"/>
     </row>
     <row r="2" spans="1:16379" s="22" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -42155,15 +42163,15 @@
       <c r="AX1" s="11"/>
       <c r="AY1" s="11"/>
       <c r="AZ1" s="13"/>
-      <c r="BA1" s="59" t="s">
+      <c r="BA1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="60"/>
-      <c r="BE1" s="60"/>
-      <c r="BF1" s="60"/>
-      <c r="BG1" s="60"/>
+      <c r="BB1" s="62"/>
+      <c r="BC1" s="62"/>
+      <c r="BD1" s="62"/>
+      <c r="BE1" s="62"/>
+      <c r="BF1" s="62"/>
+      <c r="BG1" s="62"/>
     </row>
     <row r="2" spans="1:16380" s="22" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -42187,7 +42195,7 @@
       <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="61" t="s">
+      <c r="H2" s="59" t="s">
         <v>212</v>
       </c>
       <c r="I2" s="14" t="s">
@@ -58683,7 +58691,7 @@
       <c r="G3" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="H3" s="62" t="s">
+      <c r="H3" s="60" t="s">
         <v>75</v>
       </c>
       <c r="I3" s="26" t="s">
@@ -58811,7 +58819,7 @@
       <c r="G4" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="62" t="s">
+      <c r="H4" s="60" t="s">
         <v>76</v>
       </c>
       <c r="I4" s="26" t="s">
@@ -58939,7 +58947,7 @@
       <c r="G5" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="H5" s="62" t="s">
+      <c r="H5" s="60" t="s">
         <v>77</v>
       </c>
       <c r="I5" s="26" t="s">
@@ -59067,7 +59075,7 @@
       <c r="G6" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="62" t="s">
+      <c r="H6" s="60" t="s">
         <v>78</v>
       </c>
       <c r="I6" s="26" t="s">
@@ -59195,7 +59203,7 @@
       <c r="G7" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="62" t="s">
+      <c r="H7" s="60" t="s">
         <v>80</v>
       </c>
       <c r="I7" s="26" t="s">
@@ -59323,7 +59331,7 @@
       <c r="G8" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="H8" s="62" t="s">
+      <c r="H8" s="60" t="s">
         <v>99</v>
       </c>
       <c r="I8" s="26" t="s">
@@ -59451,7 +59459,7 @@
       <c r="G9" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="H9" s="62" t="s">
+      <c r="H9" s="60" t="s">
         <v>100</v>
       </c>
       <c r="I9" s="26" t="s">
@@ -59579,7 +59587,7 @@
       <c r="G10" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="H10" s="62" t="s">
+      <c r="H10" s="60" t="s">
         <v>101</v>
       </c>
       <c r="I10" s="26" t="s">
@@ -59707,7 +59715,7 @@
       <c r="G11" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="H11" s="62" t="s">
+      <c r="H11" s="60" t="s">
         <v>102</v>
       </c>
       <c r="I11" s="26" t="s">
@@ -59835,7 +59843,7 @@
       <c r="G12" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="62" t="s">
+      <c r="H12" s="60" t="s">
         <v>103</v>
       </c>
       <c r="I12" s="26" t="s">
